--- a/begunici/app_types/animals/excel_templates/import/import_group.xlsx
+++ b/begunici/app_types/animals/excel_templates/import/import_group.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tim\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tim\Desktop\begunici\begunici\app_types\animals\excel_templates\import\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E5E478B-9327-4F7C-882A-7C7259022AA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACDF26FE-46A9-467A-9968-30E2CA417397}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3308" yWindow="3308" windowWidth="16200" windowHeight="9982" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>Бирка матери</t>
   </si>
@@ -34,6 +34,12 @@
   </si>
   <si>
     <t>Дата постановки в группу (ЧЧ-ММ-ГГ)</t>
+  </si>
+  <si>
+    <t>Овчарня (число) (необязательно)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Отсек (число, обязательно если заполнена ячейка с овчарней) </t>
   </si>
 </sst>
 </file>
@@ -366,15 +372,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="18.265625" customWidth="1"/>
     <col min="2" max="2" width="25.86328125" customWidth="1"/>
     <col min="3" max="3" width="33.796875" customWidth="1"/>
+    <col min="4" max="4" width="33.265625" customWidth="1"/>
+    <col min="5" max="5" width="55.19921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -384,6 +392,12 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
